--- a/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,47 +717,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,57; 64,53</t>
+          <t>47,66; 64,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,48; 99,32</t>
+          <t>93,12; 99,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,77; 94,54</t>
+          <t>85,57; 94,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,64; 54,11</t>
+          <t>35,33; 54,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,19; 66,61</t>
+          <t>49,72; 66,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,36; 98,85</t>
+          <t>93,38; 98,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,68; 91,59</t>
+          <t>80,48; 91,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,6; 63,1</t>
+          <t>44,34; 63,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,89; 63,27</t>
+          <t>51,21; 63,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85,1; 91,89</t>
+          <t>84,56; 91,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,98; 56,46</t>
+          <t>42,92; 55,93</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,14; 42,22</t>
+          <t>30,95; 42,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,79; 91,66</t>
+          <t>82,93; 90,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,46; 84,27</t>
+          <t>73,46; 84,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,0; 41,42</t>
+          <t>28,79; 41,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,15; 40,3</t>
+          <t>29,22; 40,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,78; 95,13</t>
+          <t>88,74; 95,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,17; 84,48</t>
+          <t>75,3; 84,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,37; 48,19</t>
+          <t>35,54; 47,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,77; 39,71</t>
+          <t>31,93; 39,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87,21; 92,54</t>
+          <t>87,27; 92,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76,23; 83,28</t>
+          <t>76,28; 83,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,01; 42,92</t>
+          <t>34,35; 42,58</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,55; 38,83</t>
+          <t>23,06; 38,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,67; 82,98</t>
+          <t>69,37; 83,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,26; 68,55</t>
+          <t>55,96; 69,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,72; 40,16</t>
+          <t>27,42; 40,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,1; 35,6</t>
+          <t>20,99; 35,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,34; 83,34</t>
+          <t>69,74; 83,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,45; 72,89</t>
+          <t>58,6; 72,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,89; 35,71</t>
+          <t>23,52; 35,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,57; 34,7</t>
+          <t>23,86; 34,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71,46; 81,19</t>
+          <t>72,12; 81,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,16; 68,25</t>
+          <t>58,63; 68,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,72; 35,61</t>
+          <t>26,88; 35,75</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 18,34</t>
+          <t>8,62; 18,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,56; 74,42</t>
+          <t>59,18; 74,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,51; 49,64</t>
+          <t>34,06; 49,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,58; 30,45</t>
+          <t>16,72; 30,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,47</t>
+          <t>6,34; 14,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,49; 71,44</t>
+          <t>57,11; 70,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,99; 51,02</t>
+          <t>35,53; 51,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,89; 38,56</t>
+          <t>24,58; 39,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 14,64</t>
+          <t>8,97; 14,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,37; 70,53</t>
+          <t>60,87; 70,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,87; 47,38</t>
+          <t>37,21; 47,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,8; 32,46</t>
+          <t>22,35; 32,17</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,18; 35,0</t>
+          <t>28,11; 35,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,61; 85,36</t>
+          <t>79,53; 85,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,57; 71,12</t>
+          <t>64,51; 71,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,45; 34,53</t>
+          <t>26,33; 34,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,03; 33,54</t>
+          <t>26,77; 33,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,08; 86,23</t>
+          <t>80,5; 85,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,34; 72,76</t>
+          <t>66,23; 72,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,04; 38,42</t>
+          <t>31,17; 38,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,41; 33,2</t>
+          <t>28,56; 33,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81,2; 84,96</t>
+          <t>81,24; 84,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66,74; 71,08</t>
+          <t>66,62; 71,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,1; 35,55</t>
+          <t>30,09; 35,55</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>43890</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>101458</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>91045</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25385</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51757</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>108546</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85120</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>32886</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>95647</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>210003</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>176164</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>58271</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>37440; 51033</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>96956; 103454</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85861; 94912</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20187; 31001</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>43980; 59074</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>104627; 110757</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>79088; 90287</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>26991; 38416</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>85538; 106094</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>204867; 213097</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>167945; 182444</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>50646; 66000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>69061</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>139670</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>122949</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>55124</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64941</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>178384</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>166151</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>74940</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>134001</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>318054</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>289100</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>130064</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>57961; 79250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>132146; 144949</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>113335; 130504</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45390; 64754</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>55145; 75591</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>171468; 184107</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>155909; 175317</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>64145; 85642</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>120041; 149350</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>307703; 326137</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>275617; 300318</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>116164; 143984</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>26134</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74941</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>88093</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>58675</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28462</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78816</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84693</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>62250</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>54595</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>153758</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>172786</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>120925</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>19944; 33564</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67969; 82165</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79547; 98109</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>47688; 70490</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21677; 36364</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>71000; 84671</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>75336; 92841</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>49984; 75049</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>45266; 65745</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>144086; 162922</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>158707; 185397</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>103871; 138124</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>20011</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>77737</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48859</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>65500</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14879</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84054</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>55709</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>91058</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>34891</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>161791</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>104567</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>156558</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13023; 27393</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68361; 86172</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>40622; 59013</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45946; 83141</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>9387; 20738</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>74860; 92334</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>45430; 65223</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>75083; 120006</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>26829; 44382</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>150097; 173927</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>91956; 117298</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>129720; 186701</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>159096</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>393806</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>350945</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>204684</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>261135</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>319134</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>843606</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>742618</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>465819</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>141510; 176257</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>379315; 407294</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>332904; 368716</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>174745; 229342</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>141508; 176911</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>433225; 461879</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>372009; 409489</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>236671; 291279</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>294665; 343019</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>824703; 862665</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>717982; 767086</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>428080; 505781</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,66; 64,96</t>
+          <t>47,19; 64,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,12; 99,36</t>
+          <t>93,55; 99,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,57; 94,59</t>
+          <t>85,49; 94,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,33; 54,26</t>
+          <t>34,89; 54,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,72; 66,78</t>
+          <t>50,19; 67,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,38; 98,85</t>
+          <t>93,04; 98,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,48; 91,88</t>
+          <t>80,81; 91,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,34; 63,12</t>
+          <t>43,56; 63,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,21; 63,52</t>
+          <t>50,5; 63,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94,77; 98,58</t>
+          <t>94,91; 98,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84,56; 91,86</t>
+          <t>84,83; 91,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,92; 55,93</t>
+          <t>42,11; 55,85</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,95; 42,32</t>
+          <t>31,16; 42,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,93; 90,97</t>
+          <t>82,85; 91,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,46; 84,59</t>
+          <t>74,24; 84,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,79; 41,07</t>
+          <t>29,83; 41,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,22; 40,05</t>
+          <t>29,04; 40,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,74; 95,28</t>
+          <t>88,45; 95,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,3; 84,68</t>
+          <t>74,85; 84,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,54; 47,45</t>
+          <t>35,34; 48,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,93; 39,72</t>
+          <t>31,78; 39,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87,27; 92,5</t>
+          <t>87,21; 92,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76,28; 83,12</t>
+          <t>76,35; 83,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,35; 42,58</t>
+          <t>34,29; 43,26</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,06; 38,81</t>
+          <t>21,91; 38,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,37; 83,86</t>
+          <t>68,54; 83,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,96; 69,02</t>
+          <t>55,09; 68,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,42; 40,54</t>
+          <t>27,45; 39,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,99; 35,22</t>
+          <t>20,76; 34,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,74; 83,16</t>
+          <t>70,58; 84,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,6; 72,21</t>
+          <t>59,02; 72,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,52; 35,32</t>
+          <t>23,92; 35,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,86; 34,65</t>
+          <t>23,63; 34,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,12; 81,55</t>
+          <t>71,12; 81,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58,63; 68,48</t>
+          <t>59,24; 68,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,88; 35,75</t>
+          <t>27,38; 36,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 18,13</t>
+          <t>9,3; 18,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,18; 74,59</t>
+          <t>59,84; 73,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,06; 49,48</t>
+          <t>33,15; 48,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,72; 30,25</t>
+          <t>16,09; 30,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 14,0</t>
+          <t>6,7; 14,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,11; 70,45</t>
+          <t>57,22; 70,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,53; 51,01</t>
+          <t>36,87; 52,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,58; 39,28</t>
+          <t>24,05; 38,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 14,83</t>
+          <t>8,69; 14,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,87; 70,53</t>
+          <t>60,44; 70,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,21; 47,47</t>
+          <t>37,09; 47,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,35; 32,17</t>
+          <t>22,06; 32,34</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,11; 35,02</t>
+          <t>28,48; 34,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,53; 85,39</t>
+          <t>79,67; 85,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,51; 71,45</t>
+          <t>64,84; 71,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,33; 34,56</t>
+          <t>26,65; 34,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,77; 33,47</t>
+          <t>27,52; 34,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,5; 85,83</t>
+          <t>81,05; 86,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,23; 72,9</t>
+          <t>66,42; 72,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,17; 38,36</t>
+          <t>30,85; 38,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,24</t>
+          <t>28,59; 33,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81,24; 84,98</t>
+          <t>81,03; 84,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66,62; 71,17</t>
+          <t>66,66; 71,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,09; 35,55</t>
+          <t>29,96; 35,62</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37440; 51033</t>
+          <t>37070; 50580</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96956; 103454</t>
+          <t>97406; 103464</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85861; 94912</t>
+          <t>85781; 95044</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20187; 31001</t>
+          <t>19935; 31257</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43980; 59074</t>
+          <t>44399; 59544</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>104627; 110757</t>
+          <t>104245; 110766</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79088; 90287</t>
+          <t>79407; 89718</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26991; 38416</t>
+          <t>26514; 38862</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85538; 106094</t>
+          <t>84348; 106102</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>204867; 213097</t>
+          <t>205169; 213317</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167945; 182444</t>
+          <t>168466; 182458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50646; 66000</t>
+          <t>49687; 65896</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57961; 79250</t>
+          <t>58346; 79311</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>132146; 144949</t>
+          <t>132017; 145959</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113335; 130504</t>
+          <t>114540; 129840</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45390; 64754</t>
+          <t>47039; 65794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55145; 75591</t>
+          <t>54800; 75796</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>171468; 184107</t>
+          <t>170913; 184130</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>155909; 175317</t>
+          <t>154977; 174746</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64145; 85642</t>
+          <t>63773; 86662</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120041; 149350</t>
+          <t>119472; 148354</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>307703; 326137</t>
+          <t>307487; 326321</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>275617; 300318</t>
+          <t>275862; 300446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>116164; 143984</t>
+          <t>115953; 146279</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19944; 33564</t>
+          <t>18948; 33039</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67969; 82165</t>
+          <t>67152; 81459</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79547; 98109</t>
+          <t>78300; 97101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47688; 70490</t>
+          <t>47730; 69091</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21677; 36364</t>
+          <t>21433; 35590</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71000; 84671</t>
+          <t>71860; 85911</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75336; 92841</t>
+          <t>75880; 92905</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49984; 75049</t>
+          <t>50818; 75129</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45266; 65745</t>
+          <t>44840; 65438</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144086; 162922</t>
+          <t>142097; 162553</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158707; 185397</t>
+          <t>160373; 184749</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>103871; 138124</t>
+          <t>105773; 139351</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13023; 27393</t>
+          <t>14049; 28014</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68361; 86172</t>
+          <t>69130; 85326</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40622; 59013</t>
+          <t>39535; 57896</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45946; 83141</t>
+          <t>44220; 83416</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9387; 20738</t>
+          <t>9924; 20904</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74860; 92334</t>
+          <t>75002; 92935</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45430; 65223</t>
+          <t>47145; 66972</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75083; 120006</t>
+          <t>73455; 118793</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26829; 44382</t>
+          <t>25991; 44392</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>150097; 173927</t>
+          <t>149051; 172974</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91956; 117298</t>
+          <t>91647; 117750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>129720; 186701</t>
+          <t>128032; 187687</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>141510; 176257</t>
+          <t>143346; 175521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>379315; 407294</t>
+          <t>380002; 407906</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>332904; 368716</t>
+          <t>334612; 370677</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>174745; 229342</t>
+          <t>176846; 228486</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>141508; 176911</t>
+          <t>145465; 180130</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>433225; 461879</t>
+          <t>436171; 462974</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>372009; 409489</t>
+          <t>373103; 409824</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>236671; 291279</t>
+          <t>234238; 289888</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>294665; 343019</t>
+          <t>295036; 343331</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>824703; 862665</t>
+          <t>822566; 861399</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>717982; 767086</t>
+          <t>718387; 767403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>428080; 505781</t>
+          <t>426337; 506888</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>58,51%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>86,62%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53,78%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>55,87%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>97,44%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>90,74%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44,43%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>58,51%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86,62%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,19; 64,39</t>
+          <t>50,19; 66,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,55; 99,37</t>
+          <t>93,36; 98,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,49; 94,73</t>
+          <t>80,68; 91,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,89; 54,71</t>
+          <t>44,21; 63,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,19; 67,31</t>
+          <t>47,57; 64,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,04; 98,86</t>
+          <t>93,48; 99,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,81; 91,3</t>
+          <t>84,77; 94,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,56; 63,85</t>
+          <t>32,76; 52,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,5; 63,53</t>
+          <t>50,89; 63,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94,91; 98,68</t>
+          <t>94,77; 98,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84,83; 91,87</t>
+          <t>85,1; 91,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,11; 55,85</t>
+          <t>41,65; 55,16</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>34,41%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80,25%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42,14%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>36,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>87,65%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>79,69%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>34,41%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>80,25%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,16; 42,36</t>
+          <t>29,15; 40,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,85; 91,6</t>
+          <t>88,78; 95,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,24; 84,16</t>
+          <t>75,17; 84,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,83; 41,73</t>
+          <t>35,83; 49,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,04; 40,16</t>
+          <t>31,14; 42,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,45; 95,29</t>
+          <t>82,79; 91,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,85; 84,4</t>
+          <t>74,46; 84,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,34; 48,02</t>
+          <t>30,78; 42,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,78; 39,46</t>
+          <t>31,77; 39,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87,21; 92,56</t>
+          <t>87,21; 92,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76,35; 83,15</t>
+          <t>76,23; 83,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,29; 43,26</t>
+          <t>35,17; 44,28</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77,41%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>65,87%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31,48%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>30,22%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>76,49%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>61,97%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33,74%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,87%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,91; 38,2</t>
+          <t>21,1; 35,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,54; 83,14</t>
+          <t>70,34; 83,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,09; 68,31</t>
+          <t>58,45; 72,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,45; 39,73</t>
+          <t>25,71; 37,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,76; 34,47</t>
+          <t>22,55; 38,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,58; 84,38</t>
+          <t>68,67; 82,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,02; 72,26</t>
+          <t>55,26; 68,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,92; 35,36</t>
+          <t>29,49; 41,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,63; 34,49</t>
+          <t>23,57; 34,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71,12; 81,36</t>
+          <t>71,46; 81,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,24; 68,25</t>
+          <t>59,16; 68,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,38; 36,07</t>
+          <t>28,84; 37,77</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>64,13%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43,57%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31,36%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,25%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>67,29%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>40,97%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 18,54</t>
+          <t>6,8; 14,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,84; 73,86</t>
+          <t>57,49; 71,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,15; 48,54</t>
+          <t>35,99; 51,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 30,35</t>
+          <t>25,52; 38,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,12</t>
+          <t>9,19; 18,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,22; 70,9</t>
+          <t>60,56; 74,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,87; 52,38</t>
+          <t>33,51; 49,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,05; 38,89</t>
+          <t>20,39; 29,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,69; 14,84</t>
+          <t>8,74; 14,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,44; 70,15</t>
+          <t>60,37; 70,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,09; 47,65</t>
+          <t>36,87; 47,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,06; 32,34</t>
+          <t>24,52; 33,32</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>31,61%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>82,57%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>68,01%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30,85%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,48; 34,87</t>
+          <t>27,03; 33,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,67; 85,52</t>
+          <t>81,08; 86,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64,84; 71,83</t>
+          <t>66,34; 72,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,65; 34,43</t>
+          <t>31,94; 39,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,52; 34,08</t>
+          <t>28,18; 35,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,05; 86,03</t>
+          <t>79,61; 85,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,42; 72,96</t>
+          <t>64,57; 71,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,85; 38,18</t>
+          <t>29,0; 35,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,59; 33,27</t>
+          <t>28,41; 33,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81,03; 84,86</t>
+          <t>81,2; 84,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66,66; 71,2</t>
+          <t>66,74; 71,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,96; 35,62</t>
+          <t>31,41; 36,5</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51757</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>108546</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>85120</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26842</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>43890</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>101458</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>91045</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25385</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>51757</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>108546</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85120</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32886</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58271</t>
+          <t>48912</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37070; 50580</t>
+          <t>44400; 58927</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97406; 103464</t>
+          <t>104607; 110759</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85781; 95044</t>
+          <t>79283; 90008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19935; 31257</t>
+          <t>22065; 31572</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44399; 59544</t>
+          <t>37374; 50696</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>104245; 110766</t>
+          <t>97333; 103416</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79407; 89718</t>
+          <t>85056; 94856</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26514; 38862</t>
+          <t>16957; 27095</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>84348; 106102</t>
+          <t>84990; 105672</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205169; 213317</t>
+          <t>204850; 213094</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168466; 182458</t>
+          <t>169017; 182499</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49687; 65896</t>
+          <t>42344; 56085</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>92</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>64941</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>178384</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>166151</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>65630</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>69061</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>139670</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>122949</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55124</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>64941</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>178384</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>166151</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>74940</t>
+          <t>52774</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>130064</t>
+          <t>118403</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58346; 79311</t>
+          <t>55019; 76061</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>132017; 145959</t>
+          <t>171542; 183811</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114540; 129840</t>
+          <t>155639; 174910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47039; 65794</t>
+          <t>55808; 76748</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54800; 75796</t>
+          <t>58308; 79047</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>170913; 184130</t>
+          <t>131921; 146062</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>154977; 174746</t>
+          <t>114869; 130013</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63773; 86662</t>
+          <t>44398; 61850</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119472; 148354</t>
+          <t>119435; 149297</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>307487; 326321</t>
+          <t>307478; 326269</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>275862; 300446</t>
+          <t>275454; 300896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>115953; 146279</t>
+          <t>105500; 132818</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28462</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78816</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>84693</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>63009</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>26134</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>74941</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>88093</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>58675</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28462</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78816</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84693</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62250</t>
+          <t>62693</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>120925</t>
+          <t>125702</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18948; 33039</t>
+          <t>21787; 36763</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67152; 81459</t>
+          <t>71618; 84847</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78300; 97101</t>
+          <t>75151; 93713</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47730; 69091</t>
+          <t>51458; 75371</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21433; 35590</t>
+          <t>19498; 33578</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71860; 85911</t>
+          <t>67285; 81300</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75880; 92905</t>
+          <t>78553; 97445</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50818; 75129</t>
+          <t>51759; 73581</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44840; 65438</t>
+          <t>44720; 65844</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142097; 162553</t>
+          <t>142768; 162203</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160373; 184749</t>
+          <t>160154; 184756</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>105773; 139351</t>
+          <t>108328; 141863</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>84</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14879</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>84054</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55709</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>91773</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20011</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>77737</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>48859</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>65500</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14879</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84054</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>55709</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91058</t>
+          <t>64359</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>156558</t>
+          <t>156132</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14049; 28014</t>
+          <t>10078; 21428</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69130; 85326</t>
+          <t>75359; 93633</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39535; 57896</t>
+          <t>46011; 65230</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44220; 83416</t>
+          <t>74675; 113707</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9924; 20904</t>
+          <t>13889; 27714</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75002; 92935</t>
+          <t>69964; 85974</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47145; 66972</t>
+          <t>39969; 59203</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73455; 118793</t>
+          <t>52200; 76773</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25991; 44392</t>
+          <t>26155; 43798</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>149051; 172974</t>
+          <t>148855; 173924</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91647; 117750</t>
+          <t>91123; 117074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>128032; 187687</t>
+          <t>134539; 182814</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>569</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>535</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>305</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>247254</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>159096</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>393806</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>350945</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>204684</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>160038</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>449801</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>391673</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>261135</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>465819</t>
+          <t>449149</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>143346; 175521</t>
+          <t>142875; 177263</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>380002; 407906</t>
+          <t>436342; 464031</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>334612; 370677</t>
+          <t>372627; 408700</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>176846; 228486</t>
+          <t>223101; 272696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>145465; 180130</t>
+          <t>141828; 176193</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>436171; 462974</t>
+          <t>379722; 407139</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>373103; 409824</t>
+          <t>333199; 367020</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>234238; 289888</t>
+          <t>181945; 221074</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>295036; 343331</t>
+          <t>293215; 342599</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>822566; 861399</t>
+          <t>824311; 862397</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>718387; 767403</t>
+          <t>719347; 766056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>426337; 506888</t>
+          <t>416526; 483894</t>
         </is>
       </c>
     </row>
